--- a/reports/SunCount_pasport_proekta.xlsx
+++ b/reports/SunCount_pasport_proekta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UniProject\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEB525D-0EF3-433E-B0AE-8F330DE4E03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6B60DE-81B3-48C1-A3F7-DBB46B0B6EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Тема проекта</t>
   </si>
   <si>
-    <t>SunCount — разработка веб-калькулятора для оценки срока окупаемости домашней сетевой солнечной электростанции 3–10 кВт с учётом тарифа и условий микрогенерации для владельцев частных домов Республики Адыгея и Краснодарского края</t>
-  </si>
-  <si>
     <t>Цель проекта</t>
   </si>
   <si>
@@ -58,9 +55,15 @@
     <t>Ссылка на хранилище артефактов (доступ)</t>
   </si>
   <si>
+    <t>https://github.com/NeK0ban/SunCount (ветка main). Доступ: Public</t>
+  </si>
+  <si>
     <t>Ссылка(и) на грантовые конкурсы, краудфандинг</t>
   </si>
   <si>
+    <t>Кандидаты: «Студенческий стартап» (ФСИ) — https://fasie.ru/programs/programma-studstartup/ ; «УМНИК» (ФСИ) — https://fasie.ru/programs/programma-umnik/ ; краудфандинг — https://planeta.ru</t>
+  </si>
+  <si>
     <t>Команда 👇</t>
   </si>
   <si>
@@ -79,9 +82,6 @@
     <t>Власов Кирилл</t>
   </si>
   <si>
-    <t>Аналитик данных и рынка</t>
-  </si>
-  <si>
     <t xml:space="preserve"> @sbaubruh</t>
   </si>
   <si>
@@ -97,7 +97,7 @@
     <t>Кривоносов Вячеслав</t>
   </si>
   <si>
-    <t>Разработчик веб-приложения</t>
+    <t>Технический специалист</t>
   </si>
   <si>
     <t xml:space="preserve"> @ferted01</t>
@@ -106,7 +106,7 @@
     <t>Рогочий Александр</t>
   </si>
   <si>
-    <t>Тестировщик и технический писатель</t>
+    <t>Контент-менеджер, дизайнер, технический специалист</t>
   </si>
   <si>
     <t xml:space="preserve"> @a_z_0_9_500</t>
@@ -121,13 +121,13 @@
     <t xml:space="preserve"> @ONISTEVLA</t>
   </si>
   <si>
-    <t>Кандидаты: «Студенческий стартап» (ФСИ) — https://fasie.ru/programs/programma-studstartup/ ; «УМНИК» (ФСИ) — https://fasie.ru/programs/programma-umnik/ ; краудфандинг — https://planeta.ru</t>
-  </si>
-  <si>
-    <t>Руководитель проекта (тимлид), экономист,Разработчик веб-приложения</t>
-  </si>
-  <si>
-    <t>https://github.com/NeK0ban/SunCount (ветка main). Доступ: Public</t>
+    <t>Менеджер проекта, технический специалист</t>
+  </si>
+  <si>
+    <t>Аналитик-исследователь, коммуникатор, спикер</t>
+  </si>
+  <si>
+    <t>SunCount — разработка системы поддержки принятия решений по выбору домашней сетевой солнечной электростанции 3–10 кВт с оценкой срока окупаемости с учётом тарифа и условий микрогенерации для владельцев частных домов Республики Адыгея и Краснодарского края</t>
   </si>
 </sst>
 </file>
@@ -211,11 +211,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -532,59 +532,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="4"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -593,18 +593,18 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -614,21 +614,21 @@
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
